--- a/results/Int All Data 0.3/Rando_6_permute.xlsx
+++ b/results/Int All Data 0.3/Rando_6_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8124437089254173</v>
+        <v>0.8480331938322486</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8210361535891031</v>
+        <v>0.8483542319749217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7886379549034896</v>
+        <v>0.8559911207294368</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8127420715115447</v>
+        <v>0.8496459430644623</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8105779482201677</v>
+        <v>0.8502804608309597</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8093013541683243</v>
+        <v>0.8483769075314673</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8099358719348217</v>
+        <v>0.8521915726493006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8194536384322837</v>
+        <v>0.8502880193498082</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8175652021704884</v>
+        <v>0.8456387346243814</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8175652021704884</v>
+        <v>0.8278344445682096</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8160053625702146</v>
+        <v>0.8281630412297312</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8160053625702146</v>
+        <v>0.8307615804465096</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8179013573508584</v>
+        <v>0.8260064764572028</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8210663876644972</v>
+        <v>0.8287597664019859</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.820141065830721</v>
+        <v>0.8281705997485798</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8204545454545454</v>
+        <v>0.8319852648664132</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8204545454545454</v>
+        <v>0.8244012857438379</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8210890632210429</v>
+        <v>0.8202655824833315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8155824833314769</v>
+        <v>0.8189209617618509</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8156051588880225</v>
+        <v>0.8097469089636078</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8145135496395779</v>
+        <v>0.8094334293397834</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8145135496395779</v>
+        <v>0.8094561048963289</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8180071766147383</v>
+        <v>0.7907794026383209</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8154993396241428</v>
+        <v>0.7866739334532088</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8098567063953026</v>
+        <v>0.8011317887433763</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.805690769059402</v>
+        <v>0.7957497255064208</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.809460083064144</v>
+        <v>0.7868286841812135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8091466034403195</v>
+        <v>0.7868286841812135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8091466034403195</v>
+        <v>0.7861941664147161</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.810408080454466</v>
+        <v>0.7991828843307927</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8141773944592079</v>
+        <v>0.7970187610394157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8160809477587002</v>
+        <v>0.7970187610394157</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8103324952659803</v>
+        <v>0.8205034769186703</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8097055360183314</v>
+        <v>0.8236231561192178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8097055360183314</v>
+        <v>0.8264142386582436</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8053092627659406</v>
+        <v>0.8261385516286619</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.81004924971755</v>
+        <v>0.8258250720048375</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8097584456502713</v>
+        <v>0.8283555845519788</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8205225721241824</v>
+        <v>0.8305726174752956</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8211646484095285</v>
+        <v>0.8237779068472224</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8167759336759862</v>
+        <v>0.8310937574590647</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8151783014814697</v>
+        <v>0.7770236939675064</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8268753083080056</v>
+        <v>0.7802113998376907</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8268753083080056</v>
+        <v>0.7672680330347055</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8261803223907198</v>
+        <v>0.7793389876358544</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8318834237703483</v>
+        <v>0.7710902566713874</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8185585506739017</v>
+        <v>0.7663275941632322</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8185585506739017</v>
+        <v>0.7710826981525389</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8223732157917349</v>
+        <v>0.7710826981525389</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8191855099215506</v>
+        <v>0.7678949922823544</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8167003484875006</v>
+        <v>0.7075024266823672</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8171721591903633</v>
+        <v>0.710040497748357</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8159635918081569</v>
+        <v>0.710040497748357</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8159635918081569</v>
+        <v>0.720521378673838</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8246089461037824</v>
+        <v>0.7698665722514839</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7795808602390083</v>
+        <v>0.8200237098801776</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7580072561780946</v>
+        <v>0.808840284518562</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7580072561780946</v>
+        <v>0.813289467402893</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7709959740941712</v>
+        <v>0.8429646102191175</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7713699218687842</v>
+        <v>0.8452799038874657</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7704143659596137</v>
+        <v>0.8616639880336712</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.773586954792101</v>
+        <v>0.8549977722260236</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7767595436245882</v>
+        <v>0.8689571630889676</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7764385054819152</v>
+        <v>0.8654862116703531</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7757964291965692</v>
+        <v>0.8813869484270325</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7961312317998823</v>
+        <v>0.8775798418280477</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7971623728975383</v>
+        <v>0.8769528825803987</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8061060897792913</v>
+        <v>0.8775798418280477</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8058152857120124</v>
+        <v>0.8798195503079103</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8227507439173813</v>
+        <v>0.8754232770555193</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8236987413077033</v>
+        <v>0.8692479671562465</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8236911827888548</v>
+        <v>0.81131430708273</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8236911827888548</v>
+        <v>0.8052750505227313</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8256022946071957</v>
+        <v>0.8030882516748086</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8269242397721306</v>
+        <v>0.807476966408351</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8300212434161323</v>
+        <v>0.8179805228903776</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8120168515188645</v>
+        <v>0.8405514536225196</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8069180338303391</v>
+        <v>0.8472176694301672</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8078735897395095</v>
+        <v>0.836691437391595</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.8097393504447592</v>
+        <v>0.8726815237973998</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.810993268940057</v>
+        <v>0.8321332527091323</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7929208503731522</v>
+        <v>0.8321332527091323</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7935553681396497</v>
+        <v>0.82487031172923</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7929284088920007</v>
+        <v>0.8277218624190443</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7910248555925083</v>
+        <v>0.8283563801855418</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7916593733590058</v>
+        <v>0.7981640755533632</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7983104721289562</v>
+        <v>0.7984851136960363</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7926678389001162</v>
+        <v>0.7923288990022754</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8072012793787693</v>
+        <v>0.7489215187053451</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.8024461753894626</v>
+        <v>0.7489215187053451</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.8021251372467896</v>
+        <v>0.7447480228505959</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7738626418216826</v>
+        <v>0.7447480228505959</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7738626418216826</v>
+        <v>0.7423611221615772</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7735416036790096</v>
+        <v>0.7225363206721512</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7686015148863039</v>
+        <v>0.6627675317855608</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7648473179192591</v>
+        <v>0.5626808077271932</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7699234600512388</v>
+        <v>0.5460739461833458</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7580072561780946</v>
+        <v>0.5510971786833856</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7548271088267589</v>
+        <v>0.5510971786833856</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7548271088267589</v>
+        <v>0.5557993730407523</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7605604442817816</v>
+        <v>0.5401178333306812</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.7946243018315484</v>
+        <v>0.5401178333306812</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7927736581639959</v>
+        <v>0.5488877042789173</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7786026287732921</v>
+        <v>0.5473278646786436</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7779605524879462</v>
+        <v>0.5454243113791513</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7677855926674411</v>
+        <v>0.5454243113791513</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7805061820727845</v>
+        <v>0.5454243113791513</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7358858584090512</v>
+        <v>0.5426105532835798</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7247402256416785</v>
+        <v>0.5516787868179431</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7238602549209936</v>
+        <v>0.543214836974683</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7238602549209936</v>
+        <v>0.5350643667552473</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7197245516604873</v>
+        <v>0.552237719395955</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.7166124309787885</v>
+        <v>0.5578501185494009</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.7221229890361696</v>
+        <v>0.5540354534315676</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.7186369205798577</v>
+        <v>0.5420854351319956</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.7215111468262178</v>
+        <v>0.5201720955396782</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7146145951020798</v>
+        <v>0.5374285918877202</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.7483498559903251</v>
+        <v>0.5374285918877202</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.7483498559903251</v>
+        <v>0.5449672198972042</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.7477228967426762</v>
+        <v>0.5278014257753449</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.7328274429928552</v>
+        <v>0.5278014257753449</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.7262181149849625</v>
+        <v>0.5278014257753449</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.7256516238881021</v>
+        <v>0.5343693808379613</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.7262861416545996</v>
+        <v>0.5346753019429372</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6618453924860366</v>
+        <v>0.5468405391213023</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5978732714860844</v>
+        <v>0.5468405391213023</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5358838693251436</v>
+        <v>0.5020053943955571</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.536824308196617</v>
+        <v>0.5042299858377226</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5311665579300797</v>
+        <v>0.501080072561781</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5311665579300797</v>
+        <v>0.5039769743646866</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.504664401763124</v>
+        <v>0.5039920914023837</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.5027759655013287</v>
+        <v>0.5039996499212323</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5030894451251532</v>
+        <v>0.5031610521458237</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5043509221392996</v>
+        <v>0.4995504670369015</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5043509221392996</v>
+        <v>0.4970426300463059</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.5034029247489776</v>
+        <v>0.4926085641996722</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5059032032207247</v>
+        <v>0.4929296023423452</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5055897235969002</v>
+        <v>0.4907579205321198</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5055746065592032</v>
+        <v>0.4859423483920245</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.515851407475773</v>
+        <v>0.4932581990038668</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5082371942778035</v>
+        <v>0.4986780548350652</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5082976624285919</v>
+        <v>0.498088888181659</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5101785401715386</v>
+        <v>0.4974543704151616</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5085960250147192</v>
+        <v>0.4974543704151616</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5067151472717725</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5069303661505657</v>
+        <v>0.5006194007288003</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5085279983450821</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5148580589723597</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5119460401317569</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5088943876008465</v>
+        <v>0.5003134796238244</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5079690657670703</v>
+        <v>0.5009404388714733</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.504154400649237</v>
+        <v>0.5009404388714733</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5060277198733352</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.498647820759671</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.498647820759671</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
